--- a/conference_registration_forms/025_hospital_communication_excellence_forum_registration--conference_registration_forms.xlsx
+++ b/conference_registration_forms/025_hospital_communication_excellence_forum_registration--conference_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'in_person',_'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'in_person', 'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'virtual',_'label':_'virtual'}</t>
+          <t>virtual</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'virtual', 'label': 'Virtual'}</t>
+          <t>Virtual</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'vegetarian',_'label':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'vegetarian', 'label': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'vegan',_'label':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'vegan', 'label': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'gluten_free',_'label':_'gluten_free'}</t>
+          <t>gluten_free</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'gluten_free', 'label': 'Gluten Free'}</t>
+          <t>Gluten Free</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'wheelchair_accessible',_'label':_'wheelchair_accessible'}</t>
+          <t>wheelchair_accessible</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'wheelchair_accessible', 'label': 'Wheelchair Accessible'}</t>
+          <t>Wheelchair Accessible</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'audio_desktop',_'label':_'audio_descriptive_support'}</t>
+          <t>audio_descriptive_support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'audio_desktop', 'label': 'Audio Descriptive Support'}</t>
+          <t>Audio Descriptive Support</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'visual_alternate',_'label':_'visual_alternative_support'}</t>
+          <t>visual_alternative_support</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'visual_alternate', 'label': 'Visual Alternative Support'}</t>
+          <t>Visual Alternative Support</t>
         </is>
       </c>
     </row>
